--- a/erp-server/erp-server-wms/src/main/resources/excel/fbaInventory.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/fbaInventory.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>平台唯一编号</t>
   </si>
@@ -64,7 +64,19 @@
     <t>不可售数量</t>
   </si>
   <si>
-    <t>库龄</t>
+    <t>库龄0-90</t>
+  </si>
+  <si>
+    <t>库龄91-180</t>
+  </si>
+  <si>
+    <t>库龄181-270</t>
+  </si>
+  <si>
+    <t>库龄271-365</t>
+  </si>
+  <si>
+    <t>库龄365天以上</t>
   </si>
   <si>
     <t>更新时间</t>
@@ -118,7 +130,19 @@
     <t>{.unsellableQty}</t>
   </si>
   <si>
-    <t>{.inventoryAge}</t>
+    <t>{.inventoryAge0To90Days}</t>
+  </si>
+  <si>
+    <t>{.inventoryAge91To180Days}</t>
+  </si>
+  <si>
+    <t>{.inventoryAge181To270Days}</t>
+  </si>
+  <si>
+    <t>{.inventoryAge271To365Days}</t>
+  </si>
+  <si>
+    <t>{.inventoryAge365PlusDays}</t>
   </si>
   <si>
     <t>{.updateTime}</t>
@@ -1117,7 +1141,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.75" customWidth="1"/>
@@ -1136,15 +1160,17 @@
     <col min="14" max="14" width="6.75" customWidth="1"/>
     <col min="15" max="15" width="10.125" customWidth="1"/>
     <col min="16" max="16" width="10.375" customWidth="1"/>
-    <col min="17" max="17" width="13.375" customWidth="1"/>
-    <col min="18" max="18" width="19" customWidth="1"/>
-    <col min="19" max="19" width="31.25" customWidth="1"/>
-    <col min="21" max="21" width="17.25" customWidth="1"/>
+    <col min="17" max="17" width="8.25" customWidth="1"/>
+    <col min="18" max="18" width="10.125" customWidth="1"/>
+    <col min="19" max="19" width="10.625" customWidth="1"/>
+    <col min="20" max="20" width="11.125" customWidth="1"/>
+    <col min="21" max="21" width="11.75" customWidth="1"/>
+    <col min="22" max="22" width="14.875" customWidth="1"/>
     <col min="23" max="23" width="9.375" customWidth="1"/>
     <col min="24" max="24" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1199,61 +1225,85 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:22">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/fbaInventory.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/fbaInventory.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>平台唯一编号</t>
   </si>
@@ -64,7 +64,13 @@
     <t>不可售数量</t>
   </si>
   <si>
-    <t>库龄0-90</t>
+    <t>库龄 0-30</t>
+  </si>
+  <si>
+    <t>库龄 31-60</t>
+  </si>
+  <si>
+    <t>库龄61-90</t>
   </si>
   <si>
     <t>库龄91-180</t>
@@ -130,7 +136,13 @@
     <t>{.unsellableQty}</t>
   </si>
   <si>
-    <t>{.inventoryAge0To90Days}</t>
+    <t>{.inventoryAge0To30Days}</t>
+  </si>
+  <si>
+    <t>{.inventoryAge31To60Days}</t>
+  </si>
+  <si>
+    <t>{.inventoryAge61To90Days}</t>
   </si>
   <si>
     <t>{.inventoryAge91To180Days}</t>
@@ -1141,7 +1153,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.75" customWidth="1"/>
@@ -1159,18 +1171,18 @@
     <col min="13" max="13" width="7.25" customWidth="1"/>
     <col min="14" max="14" width="6.75" customWidth="1"/>
     <col min="15" max="15" width="10.125" customWidth="1"/>
-    <col min="16" max="16" width="10.375" customWidth="1"/>
-    <col min="17" max="17" width="8.25" customWidth="1"/>
-    <col min="18" max="18" width="10.125" customWidth="1"/>
-    <col min="19" max="19" width="10.625" customWidth="1"/>
-    <col min="20" max="20" width="11.125" customWidth="1"/>
-    <col min="21" max="21" width="11.75" customWidth="1"/>
-    <col min="22" max="22" width="14.875" customWidth="1"/>
-    <col min="23" max="23" width="9.375" customWidth="1"/>
-    <col min="24" max="24" width="14.375" customWidth="1"/>
+    <col min="16" max="18" width="10.375" customWidth="1"/>
+    <col min="19" max="19" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.125" customWidth="1"/>
+    <col min="21" max="21" width="10.625" customWidth="1"/>
+    <col min="22" max="22" width="11.125" customWidth="1"/>
+    <col min="23" max="23" width="11.75" customWidth="1"/>
+    <col min="24" max="24" width="14.875" customWidth="1"/>
+    <col min="25" max="25" width="9.375" customWidth="1"/>
+    <col min="26" max="26" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1237,73 +1249,85 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:24">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="Q2" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="R2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="T2" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/fbaInventory.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/fbaInventory.xlsx
@@ -14,10 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
-  <si>
-    <t>平台唯一编号</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>仓库名称</t>
   </si>
@@ -52,7 +49,7 @@
     <t>入库中数量</t>
   </si>
   <si>
-    <t>FBI可售</t>
+    <t>FBA可售</t>
   </si>
   <si>
     <t>预留</t>
@@ -61,7 +58,7 @@
     <t>调查中数量</t>
   </si>
   <si>
-    <t>不可售数量</t>
+    <t>FBA不可售数量</t>
   </si>
   <si>
     <t>库龄 0-30</t>
@@ -88,16 +85,13 @@
     <t>更新时间</t>
   </si>
   <si>
-    <t>{.fbaShipmentId}</t>
-  </si>
-  <si>
     <t>{.warehouseName}</t>
   </si>
   <si>
     <t>{.asin}</t>
   </si>
   <si>
-    <t>{.mSku}</t>
+    <t>{.msku}</t>
   </si>
   <si>
     <t>{.fnSku}</t>
@@ -1153,36 +1147,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="12.75" customWidth="1"/>
-    <col min="2" max="2" width="16.375" customWidth="1"/>
-    <col min="3" max="3" width="11.875" customWidth="1"/>
-    <col min="4" max="4" width="10.125" customWidth="1"/>
-    <col min="5" max="5" width="8.75" customWidth="1"/>
-    <col min="6" max="6" width="13.625" customWidth="1"/>
-    <col min="7" max="7" width="32.125" customWidth="1"/>
-    <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="9.75" customWidth="1"/>
-    <col min="10" max="10" width="10.875" customWidth="1"/>
-    <col min="11" max="11" width="9.25" customWidth="1"/>
-    <col min="12" max="12" width="10.25" customWidth="1"/>
-    <col min="13" max="13" width="7.25" customWidth="1"/>
-    <col min="14" max="14" width="6.75" customWidth="1"/>
-    <col min="15" max="15" width="10.125" customWidth="1"/>
-    <col min="16" max="18" width="10.375" customWidth="1"/>
-    <col min="19" max="19" width="9" customWidth="1"/>
-    <col min="20" max="20" width="10.125" customWidth="1"/>
-    <col min="21" max="21" width="10.625" customWidth="1"/>
-    <col min="22" max="22" width="11.125" customWidth="1"/>
-    <col min="23" max="23" width="11.75" customWidth="1"/>
-    <col min="24" max="24" width="14.875" customWidth="1"/>
-    <col min="25" max="25" width="9.375" customWidth="1"/>
-    <col min="26" max="26" width="14.375" customWidth="1"/>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="11.875" customWidth="1"/>
+    <col min="3" max="3" width="10.125" customWidth="1"/>
+    <col min="4" max="4" width="8.75" customWidth="1"/>
+    <col min="5" max="5" width="13.625" customWidth="1"/>
+    <col min="6" max="6" width="32.125" customWidth="1"/>
+    <col min="7" max="7" width="11.5" customWidth="1"/>
+    <col min="8" max="8" width="9.75" customWidth="1"/>
+    <col min="9" max="9" width="10.875" customWidth="1"/>
+    <col min="10" max="10" width="9.25" customWidth="1"/>
+    <col min="11" max="11" width="10.25" customWidth="1"/>
+    <col min="12" max="12" width="7.25" customWidth="1"/>
+    <col min="13" max="13" width="6.75" customWidth="1"/>
+    <col min="14" max="14" width="10.125" customWidth="1"/>
+    <col min="15" max="15" width="12.5" customWidth="1"/>
+    <col min="16" max="17" width="10.375" customWidth="1"/>
+    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="19" max="19" width="10.125" customWidth="1"/>
+    <col min="20" max="20" width="10.625" customWidth="1"/>
+    <col min="21" max="21" width="11.125" customWidth="1"/>
+    <col min="22" max="22" width="11.75" customWidth="1"/>
+    <col min="23" max="23" width="14.875" customWidth="1"/>
+    <col min="24" max="24" width="9.375" customWidth="1"/>
+    <col min="25" max="25" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1252,82 +1246,76 @@
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:23">
+      <c r="A2" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
